--- a/assessment_forms/027_present_tense_grammar_quiz--assessment_forms.xlsx
+++ b/assessment_forms/027_present_tense_grammar_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>present tense verb choice 1</t>
+          <t>What is the correct form of the verb 'go' in present simple tense?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>present tense verb choice 2</t>
+          <t>Which is the correct form of the verb 'eat' in present simple tense?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_3</t>
+          <t>present_tense_subjunctive_mood_choice</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>present tense verb choice 3</t>
+          <t>Is the sentence 'If it rains, I will study.' in the present subjunctive mood?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_4</t>
+          <t>present_tense_aspects_of_the_tense_choice</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>present tense verb choice 4</t>
+          <t>What are the three main aspects of the present tense?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_5</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>present tense verb choice 5</t>
+          <t>What is the current date and time?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_6</t>
+          <t>present_tense_verb_form_choice</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>present tense verb choice 6</t>
+          <t>What is the correct form of the verb 'read' in present simple tense?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>present_tense_subjunctive_mood_choice</t>
+          <t>present_tense_verb_form_choice_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>present tenses subjunctive mood choice</t>
+          <t>Which is the correct form of the verb 'write' in present simple tense?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice</t>
+          <t>present_tense_aspects_of_the_tense_choice_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>present tense aspects of the tense choice</t>
+          <t>What are the two main tenses in present perfect tense?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice_2</t>
+          <t>present_tense_aspects_of_the_tense_choice_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>present tense aspects of the tense choice 2</t>
+          <t>Which tense is used for actions that started in the past and still continue to the present?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice_3</t>
+          <t>present_tense_aspects_of_the_tense_choice_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>present tense aspects of the tense choice 3</t>
+          <t>What is the tense used for actions that started in the past and are completed?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice_4</t>
+          <t>present_tense_aspects_of_the_tense_choice_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>present tense aspects of the tense choice 4</t>
+          <t>Which tense is used for actions that are completed in the future?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,297 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>present tense verb form choice</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>present tense verb form choice 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>present tense verb form choice 3</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>present tense aspects of the tense choice 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>present tense aspects of the tense choice 3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>present tense aspects of the tense choice 4</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>present tense aspects of the tense choice 5</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>present tense aspects of the tense choice 6</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>i_go</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>I go</t>
         </is>
       </c>
     </row>
@@ -1148,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>you_go</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>you go</t>
         </is>
       </c>
     </row>
@@ -1165,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>he/she/it_goes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>he/she/it goes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>i_eat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>I eat</t>
         </is>
       </c>
     </row>
@@ -1199,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>you_eat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>you eat</t>
         </is>
       </c>
     </row>
@@ -1216,658 +940,335 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>he/she/it_eats</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>he/she/it eats</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_3_choices</t>
+          <t>present_tense_subjunctive_mood_choice_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_3_choices</t>
+          <t>present_tense_subjunctive_mood_choice_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_3_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>present_simple</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Present Simple</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_4_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>present_continuous</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Present Continuous</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_4_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>present_perfect</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Present Perfect</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_4_choices</t>
+          <t>present_tense_verb_form_choice_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>i_read</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>I read</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_5_choices</t>
+          <t>present_tense_verb_form_choice_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>you_read</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>you read</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_5_choices</t>
+          <t>present_tense_verb_form_choice_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>he/she/it_reads</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>he/she/it reads</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_5_choices</t>
+          <t>present_tense_verb_form_choice_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>i_write</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>I write</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_6_choices</t>
+          <t>present_tense_verb_form_choice_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>you_write</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>you write</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_6_choices</t>
+          <t>present_tense_verb_form_choice_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>he/she/it_writes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>he/she/it writes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>present_tense_verb_choice_6_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>present_perfect</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Present Perfect</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>present_tense_subjunctive_mood_choice_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>present_continuous</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Present Continuous</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>present_tense_subjunctive_mood_choice_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>present_continuous</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Present Continuous</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>past_simple</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Past Simple</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>past_perfect</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Past Perfect</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice_2_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>past_simple</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Past Simple</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice_2_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_5_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>future_simple</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Future Simple</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>present_tense_aspects_of_the_tense_choice_3_choices</t>
+          <t>present_tense_aspects_of_the_tense_choice_5_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>future_perfect</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_3_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_4_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_4_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>present_tense_verb_form_choice_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_3_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_3_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_4_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_4_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_5_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_5_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_6_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>present_tense_aspects_of_the_tense_choice_6_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Future Perfect</t>
         </is>
       </c>
     </row>
